--- a/excel/Batch_10_Leads_Tracker.xlsx
+++ b/excel/Batch_10_Leads_Tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -848,7 +848,7 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H6" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I6" t="str">
         <v/>

--- a/excel/Batch_10_Leads_Tracker.xlsx
+++ b/excel/Batch_10_Leads_Tracker.xlsx
@@ -1359,10 +1359,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J12" t="str">
         <v>Re: A clearer salon and beauty website for Tofem</v>
@@ -1444,10 +1444,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J13" t="str">
         <v>Re: A warmer, more reliable website for The Parish Nursery</v>
@@ -1530,10 +1530,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J14" t="str">
         <v>Re: A fresh website concept for Brazilian Gourmet</v>
@@ -1616,10 +1616,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J15" t="str">
         <v>Re: A clearer recruitment website for Renaissance Personnel</v>
@@ -1702,10 +1702,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J16" t="str">
         <v>Re: A cleaner quote-focused website for Pack Edge Printing</v>
@@ -1786,10 +1786,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H17" t="str">
-        <v>Draft</v>
+        <v>Mail Not Found</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J17" t="str">
         <v>Re: A stronger project website for Citywide Drives and Patios</v>
@@ -1870,10 +1870,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J18" t="str">
         <v>Re: A clearer website concept for Mason James Accountancy</v>
@@ -1954,10 +1954,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J19" t="str">
         <v>Re: A faster enquiry website for ABX Couriers</v>
@@ -2038,10 +2038,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J20" t="str">
         <v>Re: A clearer transformation website for Bowes Consulting</v>
@@ -2122,10 +2122,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J21" t="str">
         <v>Re: A stronger IT support website for HC Technology</v>

--- a/excel/Batch_10_Leads_Tracker.xlsx
+++ b/excel/Batch_10_Leads_Tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="200" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -851,7 +851,7 @@
         <v>Bounce Back</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J6" t="str">
         <v>Re: A more reliable website concept for Your Place With Grace</v>

--- a/excel/Batch_10_Leads_Tracker.xlsx
+++ b/excel/Batch_10_Leads_Tracker.xlsx
@@ -2122,7 +2122,7 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H21" t="str">
-        <v>Sent</v>
+        <v>Replied</v>
       </c>
       <c r="I21" t="str">
         <v>2026-09-17</v>

--- a/excel/Batch_10_Leads_Tracker.xlsx
+++ b/excel/Batch_10_Leads_Tracker.xlsx
@@ -532,10 +532,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N2" t="str">
         <v>Final follow-up: Londonist Global</v>
@@ -616,10 +616,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N3" t="str">
         <v>Final follow-up: ADFM Security</v>
@@ -700,10 +700,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N4" t="str">
         <v>Final follow-up: SAI Distribution</v>
@@ -784,10 +784,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N5" t="str">
         <v>Final follow-up: Avrasons</v>
@@ -954,10 +954,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N7" t="str">
         <v>Final follow-up: SBL Financial</v>
@@ -1038,10 +1038,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N8" t="str">
         <v>Final follow-up: Tek Dynamics Solutions</v>
@@ -1122,10 +1122,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N9" t="str">
         <v>Final follow-up: SRW Consulting</v>
@@ -1208,10 +1208,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N10" t="str">
         <v>Final follow-up: Arts Outburst</v>
@@ -1293,10 +1293,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N11" t="str">
         <v>Final follow-up: Secure Storage Co</v>
@@ -1379,10 +1379,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N12" t="str">
         <v>Final follow-up: Tofem Salon &amp; Beauty Cosmetics</v>
@@ -1464,10 +1464,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N13" t="str">
         <v>Final follow-up: The Parish Nursery</v>
@@ -1550,10 +1550,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N14" t="str">
         <v>Final follow-up: Brazilian Gourmet</v>
@@ -1636,10 +1636,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N15" t="str">
         <v>Final follow-up: Renaissance Personnel</v>
@@ -1702,7 +1702,7 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H16" t="str">
-        <v>Sent</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I16" t="str">
         <v>2026-09-17</v>
@@ -1890,10 +1890,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N18" t="str">
         <v>Final follow-up: Mason James Accountancy</v>
@@ -1974,10 +1974,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N19" t="str">
         <v>Final follow-up: ABX Couriers</v>
@@ -2058,10 +2058,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N20" t="str">
         <v>Final follow-up: Bowes Consulting</v>
